--- a/ImportExportExcellApi/Templates/HU_WORKING_BASE.xlsx
+++ b/ImportExportExcellApi/Templates/HU_WORKING_BASE.xlsx
@@ -1388,21 +1388,10 @@
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.1428571428571" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="23.0095238095238" customWidth="1"/>
-    <col min="3" max="4" width="16.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="16.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="26.7142857142857" customWidth="1"/>
-    <col min="7" max="7" width="19.3238095238095" customWidth="1"/>
-    <col min="8" max="9" width="22.1809523809524" customWidth="1"/>
-    <col min="10" max="10" width="26.7238095238095" customWidth="1"/>
-    <col min="11" max="11" width="17.7142857142857" customWidth="1"/>
+    <col min="2" max="11" width="22.7142857142857" customWidth="1"/>
     <col min="12" max="12" width="23.5333333333333" customWidth="1"/>
-    <col min="13" max="13" width="15.1428571428571" customWidth="1"/>
-    <col min="14" max="14" width="17.5714285714286" customWidth="1"/>
-    <col min="15" max="15" width="16.5714285714286" customWidth="1"/>
-    <col min="16" max="16" width="16.2857142857143" customWidth="1"/>
-    <col min="17" max="17" width="15.1428571428571" customWidth="1"/>
-    <col min="18" max="18" width="14.1047619047619" customWidth="1"/>
+    <col min="13" max="13" width="25.7142857142857" customWidth="1"/>
+    <col min="14" max="18" width="22.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:18">

--- a/ImportExportExcellApi/Templates/HU_WORKING_BASE.xlsx
+++ b/ImportExportExcellApi/Templates/HU_WORKING_BASE.xlsx
@@ -1609,7 +1609,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="G6"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
